--- a/research/traditional_assets/database/data/qatar/qatar_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_chemical_basic.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.133</v>
+        <v>0.138</v>
       </c>
       <c r="E2">
-        <v>0.1</v>
+        <v>0.118</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.9925404061334439</v>
+        <v>0.9910442073170733</v>
       </c>
       <c r="J2">
-        <v>0.9925404061334439</v>
+        <v>0.9910442073170733</v>
       </c>
       <c r="K2">
-        <v>450.5</v>
+        <v>520.2</v>
       </c>
       <c r="L2">
-        <v>0.9334852880232076</v>
+        <v>0.9912347560975612</v>
       </c>
       <c r="M2">
-        <v>138</v>
+        <v>379.6</v>
       </c>
       <c r="N2">
-        <v>0.01913344887348354</v>
+        <v>0.05171521211956078</v>
       </c>
       <c r="O2">
-        <v>0.3063263041065483</v>
+        <v>0.7297193387158785</v>
       </c>
       <c r="P2">
-        <v>138</v>
+        <v>379.6</v>
       </c>
       <c r="Q2">
-        <v>0.01913344887348354</v>
+        <v>0.05171521211956078</v>
       </c>
       <c r="R2">
-        <v>0.3063263041065483</v>
+        <v>0.7297193387158785</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.63</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="V2">
-        <v>0.0002259965337954939</v>
+        <v>0.01091250919593472</v>
       </c>
       <c r="W2">
-        <v>0.106544001135208</v>
+        <v>0.1134569247546347</v>
       </c>
       <c r="X2">
-        <v>0.06209824066098503</v>
+        <v>0.1077178970730865</v>
       </c>
       <c r="Y2">
-        <v>0.04444576047422297</v>
+        <v>0.005739027681548187</v>
       </c>
       <c r="Z2">
-        <v>0.1162191450933173</v>
+        <v>0.1145009021746008</v>
       </c>
       <c r="AA2">
-        <v>0.1153521974714028</v>
+        <v>0.113475455832717</v>
       </c>
       <c r="AB2">
-        <v>0.06209824066098503</v>
+        <v>0.1077178970730865</v>
       </c>
       <c r="AC2">
-        <v>0.05325395681041774</v>
+        <v>0.005757558759630479</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.63</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0002260476197740356</v>
+        <v>-0.01103290588283908</v>
       </c>
       <c r="AK2">
-        <v>-0.0003556335185682151</v>
+        <v>-0.01729125291425611</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.133</v>
+        <v>0.138</v>
       </c>
       <c r="E3">
-        <v>0.1</v>
+        <v>0.118</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,34 +722,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9925404061334439</v>
+        <v>0.9910442073170733</v>
       </c>
       <c r="J3">
-        <v>0.9925404061334439</v>
+        <v>0.9910442073170733</v>
       </c>
       <c r="K3">
-        <v>450.5</v>
+        <v>520.2</v>
       </c>
       <c r="L3">
-        <v>0.9334852880232076</v>
+        <v>0.9912347560975612</v>
       </c>
       <c r="M3">
-        <v>138</v>
+        <v>379.6</v>
       </c>
       <c r="N3">
-        <v>0.01913344887348354</v>
+        <v>0.05171521211956078</v>
       </c>
       <c r="O3">
-        <v>0.3063263041065483</v>
+        <v>0.7297193387158785</v>
       </c>
       <c r="P3">
-        <v>138</v>
+        <v>379.6</v>
       </c>
       <c r="Q3">
-        <v>0.01913344887348354</v>
+        <v>0.05171521211956078</v>
       </c>
       <c r="R3">
-        <v>0.3063263041065483</v>
+        <v>0.7297193387158785</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.63</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="V3">
-        <v>0.0002259965337954939</v>
+        <v>0.01091250919593472</v>
       </c>
       <c r="W3">
-        <v>0.106544001135208</v>
+        <v>0.1134569247546347</v>
       </c>
       <c r="X3">
-        <v>0.06209824066098503</v>
+        <v>0.1077178970730865</v>
       </c>
       <c r="Y3">
-        <v>0.04444576047422297</v>
+        <v>0.005739027681548187</v>
       </c>
       <c r="Z3">
-        <v>0.1162191450933173</v>
+        <v>0.1145009021746008</v>
       </c>
       <c r="AA3">
-        <v>0.1153521974714028</v>
+        <v>0.113475455832717</v>
       </c>
       <c r="AB3">
-        <v>0.06209824066098503</v>
+        <v>0.1077178970730865</v>
       </c>
       <c r="AC3">
-        <v>0.05325395681041774</v>
+        <v>0.005757558759630479</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.63</v>
+        <v>-80.09999999999999</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0002260476197740356</v>
+        <v>-0.01103290588283908</v>
       </c>
       <c r="AK3">
-        <v>-0.0003556335185682151</v>
+        <v>-0.01729125291425611</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/qatar/qatar_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_chemical_basic.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.138</v>
+        <v>-0.00777</v>
       </c>
       <c r="E2">
-        <v>0.118</v>
+        <v>-0.0266</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.9910442073170733</v>
+        <v>0.9855527638190956</v>
       </c>
       <c r="J2">
-        <v>0.9910442073170733</v>
+        <v>0.9855527638190956</v>
       </c>
       <c r="K2">
-        <v>520.2</v>
+        <v>314.5</v>
       </c>
       <c r="L2">
-        <v>0.9912347560975612</v>
+        <v>0.9877512562814071</v>
       </c>
       <c r="M2">
         <v>379.6</v>
       </c>
       <c r="N2">
-        <v>0.05171521211956078</v>
+        <v>0.06152050953762378</v>
       </c>
       <c r="O2">
-        <v>0.7297193387158785</v>
+        <v>1.206995230524642</v>
       </c>
       <c r="P2">
         <v>379.6</v>
       </c>
       <c r="Q2">
-        <v>0.05171521211956078</v>
+        <v>0.06152050953762378</v>
       </c>
       <c r="R2">
-        <v>0.7297193387158785</v>
+        <v>1.206995230524642</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>80.09999999999999</v>
+        <v>383.9</v>
       </c>
       <c r="V2">
-        <v>0.01091250919593472</v>
+        <v>0.06221739623681182</v>
       </c>
       <c r="W2">
-        <v>0.1134569247546347</v>
+        <v>0.06673740053050398</v>
       </c>
       <c r="X2">
-        <v>0.1077178970730865</v>
+        <v>0.08838606600800501</v>
       </c>
       <c r="Y2">
-        <v>0.005739027681548187</v>
+        <v>-0.02164866547750104</v>
       </c>
       <c r="Z2">
-        <v>0.1145009021746008</v>
+        <v>0.06873327001122528</v>
       </c>
       <c r="AA2">
-        <v>0.113475455832717</v>
+        <v>0.06774026422588723</v>
       </c>
       <c r="AB2">
-        <v>0.1077178970730865</v>
+        <v>0.08838606600800501</v>
       </c>
       <c r="AC2">
-        <v>0.005757558759630479</v>
+        <v>-0.02064580178211778</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-80.09999999999999</v>
+        <v>-383.9</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,10 +681,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.01103290588283908</v>
+        <v>-0.06634522328217889</v>
       </c>
       <c r="AK2">
-        <v>-0.01729125291425611</v>
+        <v>-0.09029117079825015</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.138</v>
+        <v>-0.00777</v>
       </c>
       <c r="E3">
-        <v>0.118</v>
+        <v>-0.0266</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,34 +722,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9910442073170733</v>
+        <v>0.9855527638190956</v>
       </c>
       <c r="J3">
-        <v>0.9910442073170733</v>
+        <v>0.9855527638190956</v>
       </c>
       <c r="K3">
-        <v>520.2</v>
+        <v>314.5</v>
       </c>
       <c r="L3">
-        <v>0.9912347560975612</v>
+        <v>0.9877512562814071</v>
       </c>
       <c r="M3">
         <v>379.6</v>
       </c>
       <c r="N3">
-        <v>0.05171521211956078</v>
+        <v>0.06152050953762378</v>
       </c>
       <c r="O3">
-        <v>0.7297193387158785</v>
+        <v>1.206995230524642</v>
       </c>
       <c r="P3">
         <v>379.6</v>
       </c>
       <c r="Q3">
-        <v>0.05171521211956078</v>
+        <v>0.06152050953762378</v>
       </c>
       <c r="R3">
-        <v>0.7297193387158785</v>
+        <v>1.206995230524642</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>80.09999999999999</v>
+        <v>383.9</v>
       </c>
       <c r="V3">
-        <v>0.01091250919593472</v>
+        <v>0.06221739623681182</v>
       </c>
       <c r="W3">
-        <v>0.1134569247546347</v>
+        <v>0.06673740053050398</v>
       </c>
       <c r="X3">
-        <v>0.1077178970730865</v>
+        <v>0.08838606600800501</v>
       </c>
       <c r="Y3">
-        <v>0.005739027681548187</v>
+        <v>-0.02164866547750104</v>
       </c>
       <c r="Z3">
-        <v>0.1145009021746008</v>
+        <v>0.06873327001122528</v>
       </c>
       <c r="AA3">
-        <v>0.113475455832717</v>
+        <v>0.06774026422588723</v>
       </c>
       <c r="AB3">
-        <v>0.1077178970730865</v>
+        <v>0.08838606600800501</v>
       </c>
       <c r="AC3">
-        <v>0.005757558759630479</v>
+        <v>-0.02064580178211778</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-80.09999999999999</v>
+        <v>-383.9</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01103290588283908</v>
+        <v>-0.06634522328217889</v>
       </c>
       <c r="AK3">
-        <v>-0.01729125291425611</v>
+        <v>-0.09029117079825015</v>
       </c>
       <c r="AL3">
         <v>0</v>
